--- a/V5/problemGenerator/timetablingTemplate.xlsx
+++ b/V5/problemGenerator/timetablingTemplate.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="corsi" sheetId="1" state="visible" r:id="rId3"/>
@@ -13,6 +13,7 @@
     <sheet name="disponibilitàProfessori" sheetId="3" state="visible" r:id="rId5"/>
     <sheet name="disponibilitàAule" sheetId="4" state="visible" r:id="rId6"/>
     <sheet name="disponibilitàScdla" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="configurazione" sheetId="6" state="visible" r:id="rId8"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -24,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="80">
   <si>
     <t xml:space="preserve">corso</t>
   </si>
@@ -243,16 +244,38 @@
   </si>
   <si>
     <t xml:space="preserve">scdla</t>
+  </si>
+  <si>
+    <t xml:space="preserve">configurazioni</t>
+  </si>
+  <si>
+    <t xml:space="preserve">valori</t>
+  </si>
+  <si>
+    <t xml:space="preserve">orario a costo minimo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DA IMPLEMENTARE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">orario nel quale inserire un ora di pausa pranzo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">valorizzare il tenere le giornate vuote?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">valorizzare il tenere le mezze giornate vuote?</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="General"/>
+    <numFmt numFmtId="165" formatCode="General"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -274,6 +297,18 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -318,12 +353,20 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2040,7 +2083,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:BD3"/>
+  <dimension ref="A1:BD10"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2551,6 +2594,242 @@
       </c>
       <c r="BD3" s="1" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="O4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="S4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="V4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="W4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="X4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD4" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G10" s="2" t="n">
+        <f aca="false">configurazione!B3</f>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Normale"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Normale"&amp;12&amp;KffffffPagina &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="18.26"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="B1" s="0" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0" t="s">
+        <v>75</v>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C2" s="0" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="s">
+        <v>77</v>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3" t="s">
+        <v>79</v>
       </c>
     </row>
   </sheetData>

--- a/V5/problemGenerator/timetablingTemplate.xlsx
+++ b/V5/problemGenerator/timetablingTemplate.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="5"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="corsi" sheetId="1" state="visible" r:id="rId3"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="80">
   <si>
     <t xml:space="preserve">corso</t>
   </si>
@@ -271,9 +271,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="General"/>
   </numFmts>
   <fonts count="6">
     <font>
@@ -362,7 +361,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2597,180 +2596,65 @@
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="C4" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="D4" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="E4" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="F4" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="G4" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H4" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="J4" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="K4" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L4" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="M4" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="N4" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="O4" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="P4" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q4" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="R4" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="S4" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="T4" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="U4" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="V4" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="W4" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="X4" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y4" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z4" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA4" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB4" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC4" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD4" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE4" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF4" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG4" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH4" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI4" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ4" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK4" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL4" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM4" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN4" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO4" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP4" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="AQ4" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR4" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS4" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT4" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU4" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV4" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW4" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX4" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY4" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="AZ4" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="BA4" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="BB4" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC4" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD4" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="A4" s="1"/>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="1"/>
+      <c r="N4" s="1"/>
+      <c r="O4" s="1"/>
+      <c r="P4" s="1"/>
+      <c r="Q4" s="1"/>
+      <c r="R4" s="1"/>
+      <c r="S4" s="1"/>
+      <c r="T4" s="1"/>
+      <c r="U4" s="1"/>
+      <c r="V4" s="1"/>
+      <c r="W4" s="1"/>
+      <c r="X4" s="1"/>
+      <c r="Y4" s="1"/>
+      <c r="Z4" s="1"/>
+      <c r="AA4" s="1"/>
+      <c r="AB4" s="1"/>
+      <c r="AC4" s="1"/>
+      <c r="AD4" s="1"/>
+      <c r="AE4" s="1"/>
+      <c r="AF4" s="1"/>
+      <c r="AG4" s="1"/>
+      <c r="AH4" s="1"/>
+      <c r="AI4" s="1"/>
+      <c r="AJ4" s="1"/>
+      <c r="AK4" s="1"/>
+      <c r="AL4" s="1"/>
+      <c r="AM4" s="1"/>
+      <c r="AN4" s="1"/>
+      <c r="AO4" s="1"/>
+      <c r="AP4" s="1"/>
+      <c r="AQ4" s="1"/>
+      <c r="AR4" s="1"/>
+      <c r="AS4" s="1"/>
+      <c r="AT4" s="1"/>
+      <c r="AU4" s="1"/>
+      <c r="AV4" s="1"/>
+      <c r="AW4" s="1"/>
+      <c r="AX4" s="1"/>
+      <c r="AY4" s="1"/>
+      <c r="AZ4" s="1"/>
+      <c r="BA4" s="1"/>
+      <c r="BB4" s="1"/>
+      <c r="BC4" s="1"/>
+      <c r="BD4" s="1"/>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G10" s="2" t="n">
-        <f aca="false">configurazione!B3</f>
-        <v>0</v>
-      </c>
+      <c r="G10" s="2"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/V5/problemGenerator/timetablingTemplate.xlsx
+++ b/V5/problemGenerator/timetablingTemplate.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="4"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="corsi" sheetId="1" state="visible" r:id="rId3"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="83">
   <si>
     <t xml:space="preserve">corso</t>
   </si>
@@ -63,6 +63,12 @@
     <t xml:space="preserve">Bau</t>
   </si>
   <si>
+    <t xml:space="preserve">sistemiDiMisura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Serpelloni</t>
+  </si>
+  <si>
     <t xml:space="preserve">aula</t>
   </si>
   <si>
@@ -259,6 +265,9 @@
   </si>
   <si>
     <t xml:space="preserve">orario nel quale inserire un ora di pausa pranzo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fascia oraria singola magari non è una buona cosa eliminarla</t>
   </si>
   <si>
     <t xml:space="preserve">valorizzare il tenere le giornate vuote?</t>
@@ -298,16 +307,17 @@
       <family val="0"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -352,7 +362,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -361,11 +371,19 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -561,10 +579,10 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12.98"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14.93"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="17.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="9.64"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="29.81"/>
@@ -623,6 +641,20 @@
         <v>11</v>
       </c>
       <c r="D4" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -647,25 +679,25 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -684,7 +716,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:BD4"/>
+  <dimension ref="A1:BD5"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -692,169 +724,169 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="AI1" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="AJ1" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="AK1" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="AL1" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="AM1" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="AN1" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="AO1" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="AP1" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="AQ1" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="AR1" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="AS1" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="AT1" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="AU1" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="AV1" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="AW1" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="AX1" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="AY1" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="AZ1" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="BA1" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="BB1" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="BC1" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="BD1" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1364,6 +1396,176 @@
         <v>1</v>
       </c>
       <c r="BD4" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="O5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="S5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="V5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="W5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="X5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD5" s="1" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1388,210 +1590,210 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="AI1" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="AJ1" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="AK1" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="AL1" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="AM1" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="AN1" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="AO1" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="AP1" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="AQ1" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="AR1" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="AS1" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="AT1" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="AU1" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="AV1" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="AW1" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="AX1" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="AY1" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="AZ1" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="BA1" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="BB1" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="BC1" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="BD1" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M2" s="1" t="n">
         <v>1</v>
@@ -1728,7 +1930,7 @@
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B3" s="1" t="n">
         <v>1</v>
@@ -1898,7 +2100,7 @@
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B4" s="1" t="n">
         <v>1</v>
@@ -2087,172 +2289,172 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="AF1" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AG1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="AH1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="AI1" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="AJ1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="AK1" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="AL1" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="AM1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="AN1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="AO1" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="AP1" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="AQ1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="AR1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="AS1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="AT1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="AU1" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="AV1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AW1" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="AX1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="AY1" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="AZ1" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="BA1" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="BB1" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="BC1" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="Z1" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="AA1" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="AB1" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="AC1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="AD1" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="AE1" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="AF1" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AG1" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="AH1" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AI1" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="AJ1" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="AK1" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="AL1" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="AM1" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="AN1" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="AO1" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="AP1" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="AQ1" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="AR1" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="AS1" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="AT1" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="AU1" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="AV1" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="AW1" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="AX1" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="AY1" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="AZ1" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="BA1" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="BB1" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="BC1" s="1" t="s">
-        <v>70</v>
-      </c>
       <c r="BD1" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2293,37 +2495,37 @@
         <v>1</v>
       </c>
       <c r="M2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X2" s="1" t="n">
         <v>1</v>
@@ -2654,7 +2856,7 @@
       <c r="BD4" s="1"/>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G10" s="2"/>
+      <c r="G10" s="3"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -2672,48 +2874,54 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40.52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="18.26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="40.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="18.26"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
-        <v>73</v>
-      </c>
-      <c r="B1" s="0" t="s">
-        <v>74</v>
+      <c r="A1" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
-        <v>75</v>
-      </c>
-      <c r="B2" s="3" t="n">
+      <c r="A2" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B2" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="C2" s="0" t="s">
-        <v>76</v>
+      <c r="C2" s="1" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
-        <v>77</v>
-      </c>
-      <c r="B3" s="3" t="n">
-        <v>0</v>
+      <c r="A3" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
-        <v>78</v>
+      <c r="A4" s="1" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="s">
-        <v>79</v>
+      <c r="A5" s="4" t="s">
+        <v>82</v>
       </c>
     </row>
   </sheetData>

--- a/V5/problemGenerator/timetablingTemplate.xlsx
+++ b/V5/problemGenerator/timetablingTemplate.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="5"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="corsi" sheetId="1" state="visible" r:id="rId3"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="81">
   <si>
     <t xml:space="preserve">corso</t>
   </si>
@@ -61,12 +61,6 @@
   </si>
   <si>
     <t xml:space="preserve">Bau</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sistemiDiMisura</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Serpelloni</t>
   </si>
   <si>
     <t xml:space="preserve">aula</t>
@@ -283,7 +277,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -305,12 +299,6 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -362,7 +350,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -371,19 +359,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -645,18 +625,7 @@
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>6</v>
-      </c>
+      <c r="D5" s="2"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -679,25 +648,25 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -724,169 +693,169 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AC1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AD1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AE1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AF1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AG1" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="AF1" s="1" t="s">
+      <c r="AH1" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="AG1" s="1" t="s">
+      <c r="AI1" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="AH1" s="1" t="s">
+      <c r="AJ1" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="AI1" s="1" t="s">
+      <c r="AK1" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="AJ1" s="1" t="s">
+      <c r="AL1" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="AK1" s="1" t="s">
+      <c r="AM1" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="AL1" s="1" t="s">
+      <c r="AN1" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="AM1" s="1" t="s">
+      <c r="AO1" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="AN1" s="1" t="s">
+      <c r="AP1" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="AO1" s="1" t="s">
+      <c r="AQ1" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="AP1" s="1" t="s">
+      <c r="AR1" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="AQ1" s="1" t="s">
+      <c r="AS1" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="AR1" s="1" t="s">
+      <c r="AT1" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="AS1" s="1" t="s">
+      <c r="AU1" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="AT1" s="1" t="s">
+      <c r="AV1" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="AU1" s="1" t="s">
+      <c r="AW1" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="AV1" s="1" t="s">
+      <c r="AX1" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="AW1" s="1" t="s">
+      <c r="AY1" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="AX1" s="1" t="s">
+      <c r="AZ1" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="AY1" s="1" t="s">
+      <c r="BA1" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="AZ1" s="1" t="s">
+      <c r="BB1" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="BA1" s="1" t="s">
+      <c r="BC1" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="BB1" s="1" t="s">
+      <c r="BD1" s="1" t="s">
         <v>71</v>
-      </c>
-      <c r="BC1" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="BD1" s="1" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -927,136 +896,136 @@
         <v>1</v>
       </c>
       <c r="M2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BD2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1064,37 +1033,37 @@
         <v>8</v>
       </c>
       <c r="B3" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H3" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I3" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L3" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M3" s="1" t="n">
         <v>1</v>
@@ -1130,103 +1099,103 @@
         <v>1</v>
       </c>
       <c r="X3" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y3" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z3" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA3" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB3" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC3" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD3" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE3" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF3" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG3" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH3" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI3" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ3" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK3" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL3" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM3" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN3" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO3" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP3" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ3" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR3" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS3" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT3" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU3" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV3" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW3" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX3" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY3" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ3" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA3" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB3" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC3" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BD3" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1234,70 +1203,70 @@
         <v>11</v>
       </c>
       <c r="B4" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H4" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I4" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L4" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M4" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N4" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O4" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P4" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q4" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R4" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S4" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T4" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U4" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V4" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W4" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X4" s="1" t="n">
         <v>1</v>
@@ -1333,241 +1302,129 @@
         <v>1</v>
       </c>
       <c r="AI4" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ4" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK4" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL4" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM4" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN4" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO4" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP4" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ4" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR4" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS4" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT4" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU4" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV4" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW4" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX4" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY4" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ4" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA4" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB4" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC4" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BD4" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="C5" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="N5" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="O5" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="P5" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q5" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="R5" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="S5" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="T5" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="U5" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="V5" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="W5" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="X5" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y5" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z5" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA5" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB5" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC5" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD5" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE5" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF5" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG5" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH5" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI5" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ5" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK5" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL5" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM5" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN5" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO5" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP5" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="AQ5" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR5" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS5" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT5" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU5" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV5" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW5" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX5" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY5" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="AZ5" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="BA5" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="BB5" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC5" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD5" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+      <c r="I5" s="1"/>
+      <c r="J5" s="1"/>
+      <c r="K5" s="1"/>
+      <c r="L5" s="1"/>
+      <c r="M5" s="1"/>
+      <c r="N5" s="1"/>
+      <c r="O5" s="1"/>
+      <c r="P5" s="1"/>
+      <c r="Q5" s="1"/>
+      <c r="R5" s="1"/>
+      <c r="S5" s="1"/>
+      <c r="T5" s="1"/>
+      <c r="U5" s="1"/>
+      <c r="V5" s="1"/>
+      <c r="W5" s="1"/>
+      <c r="X5" s="1"/>
+      <c r="Y5" s="1"/>
+      <c r="Z5" s="1"/>
+      <c r="AA5" s="1"/>
+      <c r="AB5" s="1"/>
+      <c r="AC5" s="1"/>
+      <c r="AD5" s="1"/>
+      <c r="AE5" s="1"/>
+      <c r="AF5" s="1"/>
+      <c r="AG5" s="1"/>
+      <c r="AH5" s="1"/>
+      <c r="AI5" s="1"/>
+      <c r="AJ5" s="1"/>
+      <c r="AK5" s="1"/>
+      <c r="AL5" s="1"/>
+      <c r="AM5" s="1"/>
+      <c r="AN5" s="1"/>
+      <c r="AO5" s="1"/>
+      <c r="AP5" s="1"/>
+      <c r="AQ5" s="1"/>
+      <c r="AR5" s="1"/>
+      <c r="AS5" s="1"/>
+      <c r="AT5" s="1"/>
+      <c r="AU5" s="1"/>
+      <c r="AV5" s="1"/>
+      <c r="AW5" s="1"/>
+      <c r="AX5" s="1"/>
+      <c r="AY5" s="1"/>
+      <c r="AZ5" s="1"/>
+      <c r="BA5" s="1"/>
+      <c r="BB5" s="1"/>
+      <c r="BC5" s="1"/>
+      <c r="BD5" s="1"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -1590,177 +1447,177 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AC1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AD1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AE1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AF1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AG1" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="AF1" s="1" t="s">
+      <c r="AH1" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="AG1" s="1" t="s">
+      <c r="AI1" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="AH1" s="1" t="s">
+      <c r="AJ1" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="AI1" s="1" t="s">
+      <c r="AK1" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="AJ1" s="1" t="s">
+      <c r="AL1" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="AK1" s="1" t="s">
+      <c r="AM1" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="AL1" s="1" t="s">
+      <c r="AN1" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="AM1" s="1" t="s">
+      <c r="AO1" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="AN1" s="1" t="s">
+      <c r="AP1" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="AO1" s="1" t="s">
+      <c r="AQ1" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="AP1" s="1" t="s">
+      <c r="AR1" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="AQ1" s="1" t="s">
+      <c r="AS1" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="AR1" s="1" t="s">
+      <c r="AT1" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="AS1" s="1" t="s">
+      <c r="AU1" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="AT1" s="1" t="s">
+      <c r="AV1" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="AU1" s="1" t="s">
+      <c r="AW1" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="AV1" s="1" t="s">
+      <c r="AX1" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="AW1" s="1" t="s">
+      <c r="AY1" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="AX1" s="1" t="s">
+      <c r="AZ1" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="AY1" s="1" t="s">
+      <c r="BA1" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="AZ1" s="1" t="s">
+      <c r="BB1" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="BA1" s="1" t="s">
+      <c r="BC1" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="BB1" s="1" t="s">
+      <c r="BD1" s="1" t="s">
         <v>71</v>
-      </c>
-      <c r="BC1" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="BD1" s="1" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B2" s="1" t="n">
         <v>0</v>
@@ -1796,16 +1653,16 @@
         <v>0</v>
       </c>
       <c r="M2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q2" s="1" t="n">
         <v>1</v>
@@ -1829,174 +1686,174 @@
         <v>1</v>
       </c>
       <c r="X2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BD2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B3" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H3" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I3" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L3" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M3" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N3" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O3" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P3" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q3" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R3" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S3" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T3" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U3" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V3" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W3" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X3" s="1" t="n">
         <v>1</v>
@@ -2005,13 +1862,13 @@
         <v>1</v>
       </c>
       <c r="Z3" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA3" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB3" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC3" s="1" t="n">
         <v>1</v>
@@ -2032,75 +1889,75 @@
         <v>1</v>
       </c>
       <c r="AI3" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ3" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK3" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL3" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM3" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN3" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO3" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP3" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ3" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR3" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS3" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT3" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU3" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV3" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW3" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX3" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY3" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ3" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA3" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB3" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC3" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BD3" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B4" s="1" t="n">
         <v>1</v>
@@ -2112,160 +1969,160 @@
         <v>1</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H4" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I4" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L4" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M4" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N4" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O4" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P4" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q4" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R4" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S4" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T4" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U4" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V4" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W4" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X4" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y4" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z4" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA4" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB4" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC4" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD4" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE4" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF4" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG4" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH4" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI4" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ4" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK4" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL4" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM4" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN4" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO4" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP4" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ4" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR4" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS4" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT4" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU4" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV4" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW4" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX4" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY4" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ4" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA4" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB4" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC4" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BD4" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2289,172 +2146,172 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AC1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AD1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AE1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AF1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AG1" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="AF1" s="1" t="s">
+      <c r="AH1" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="AG1" s="1" t="s">
+      <c r="AI1" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="AH1" s="1" t="s">
+      <c r="AJ1" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="AI1" s="1" t="s">
+      <c r="AK1" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="AJ1" s="1" t="s">
+      <c r="AL1" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="AK1" s="1" t="s">
+      <c r="AM1" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="AL1" s="1" t="s">
+      <c r="AN1" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="AM1" s="1" t="s">
+      <c r="AO1" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="AN1" s="1" t="s">
+      <c r="AP1" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="AO1" s="1" t="s">
+      <c r="AQ1" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="AP1" s="1" t="s">
+      <c r="AR1" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="AQ1" s="1" t="s">
+      <c r="AS1" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="AR1" s="1" t="s">
+      <c r="AT1" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="AS1" s="1" t="s">
+      <c r="AU1" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="AT1" s="1" t="s">
+      <c r="AV1" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="AU1" s="1" t="s">
+      <c r="AW1" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="AV1" s="1" t="s">
+      <c r="AX1" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="AW1" s="1" t="s">
+      <c r="AY1" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="AX1" s="1" t="s">
+      <c r="AZ1" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="AY1" s="1" t="s">
+      <c r="BA1" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="AZ1" s="1" t="s">
+      <c r="BB1" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="BA1" s="1" t="s">
+      <c r="BC1" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="BB1" s="1" t="s">
+      <c r="BD1" s="1" t="s">
         <v>71</v>
-      </c>
-      <c r="BC1" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="BD1" s="1" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2462,37 +2319,37 @@
         <v>9</v>
       </c>
       <c r="B2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M2" s="1" t="n">
         <v>0</v>
@@ -2510,16 +2367,16 @@
         <v>0</v>
       </c>
       <c r="R2" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S2" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T2" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U2" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V2" s="1" t="n">
         <v>0</v>
@@ -2528,76 +2385,76 @@
         <v>0</v>
       </c>
       <c r="X2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV2" s="1" t="n">
         <v>1</v>
@@ -2612,19 +2469,19 @@
         <v>1</v>
       </c>
       <c r="AZ2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BD2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2665,37 +2522,37 @@
         <v>1</v>
       </c>
       <c r="M3" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N3" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O3" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P3" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q3" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R3" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S3" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T3" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U3" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V3" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W3" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X3" s="1" t="n">
         <v>1</v>
@@ -2731,70 +2588,70 @@
         <v>1</v>
       </c>
       <c r="AI3" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ3" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK3" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL3" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM3" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN3" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO3" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP3" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ3" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR3" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS3" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT3" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU3" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV3" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW3" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX3" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY3" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ3" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA3" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB3" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC3" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BD3" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2883,45 +2740,45 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="B2" s="4" t="n">
+        <v>75</v>
+      </c>
+      <c r="B2" s="2" t="n">
         <v>8</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="B3" s="4" t="n">
+        <v>77</v>
+      </c>
+      <c r="B3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>78</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
-        <v>82</v>
+      <c r="A5" s="2" t="s">
+        <v>80</v>
       </c>
     </row>
   </sheetData>
